--- a/DesignerConfigs/Datas/PayRegion.xlsx
+++ b/DesignerConfigs/Datas/PayRegion.xlsx
@@ -100,7 +100,7 @@
     <t>US</t>
   </si>
   <si>
-    <t>1,2,0,13,8,9</t>
+    <t>0,1,2</t>
   </si>
   <si>
     <t>$</t>
@@ -127,7 +127,7 @@
     <t>BR</t>
   </si>
   <si>
-    <t>6,0,4,7,8,9</t>
+    <t>6,4,7</t>
   </si>
   <si>
     <t>R$</t>
@@ -260,15 +260,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <color rgb="FF333333"/>
       <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -898,11 +898,11 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1251,9 +1251,9 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3"/>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="J1" s="5"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1266,49 +1266,49 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:9">
+      <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1337,23 +1337,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="B6" s="5">
+    <row r="6" spans="2:9">
+      <c r="B6" s="4">
         <v>1</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="4">
         <v>2</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="4">
         <v>1</v>
       </c>
       <c r="H6" t="s">
@@ -1363,23 +1363,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="5">
+    <row r="7" spans="2:9">
+      <c r="B7" s="4">
         <v>2</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>2</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="4">
         <v>1.4</v>
       </c>
       <c r="H7" t="s">
@@ -1389,23 +1389,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="5">
+    <row r="8" spans="2:9">
+      <c r="B8" s="4">
         <v>3</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="4">
         <v>2</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="4">
         <v>20</v>
       </c>
       <c r="H8" t="s">
@@ -1415,23 +1415,23 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="5">
+    <row r="9" spans="2:9">
+      <c r="B9" s="4">
         <v>4</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="4">
         <v>2</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="4">
         <v>5</v>
       </c>
       <c r="H9" t="s">
@@ -1441,23 +1441,23 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="5">
+    <row r="10" spans="2:9">
+      <c r="B10" s="4">
         <v>5</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D10" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <v>2</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>1</v>
       </c>
       <c r="H10" t="s">
@@ -1467,23 +1467,23 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
-      <c r="B11" s="5">
+    <row r="11" spans="2:9">
+      <c r="B11" s="4">
         <v>6</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D11" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="4">
         <v>2</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="4">
         <v>1</v>
       </c>
       <c r="H11" t="s">
@@ -1493,23 +1493,23 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
-      <c r="B12" s="5">
+    <row r="12" spans="2:9">
+      <c r="B12" s="4">
         <v>7</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D12" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <v>2</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="4">
         <v>1</v>
       </c>
       <c r="H12" t="s">
@@ -1519,23 +1519,23 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
-      <c r="B13" s="5">
+    <row r="13" spans="2:9">
+      <c r="B13" s="4">
         <v>8</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D13" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="4">
         <v>0</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="4">
         <v>150</v>
       </c>
       <c r="H13" t="s">
@@ -1545,23 +1545,23 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="5">
+    <row r="14" spans="2:9">
+      <c r="B14" s="4">
         <v>9</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="4">
         <v>2</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="4">
         <v>1.5</v>
       </c>
       <c r="H14" t="s">
@@ -1571,8 +1571,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="5">
+    <row r="15" spans="2:9">
+      <c r="B15" s="4">
         <v>10</v>
       </c>
       <c r="C15" t="s">
@@ -1584,7 +1584,7 @@
       <c r="E15" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <v>0</v>
       </c>
       <c r="G15">
@@ -1597,8 +1597,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="5">
+    <row r="16" spans="2:9">
+      <c r="B16" s="4">
         <v>11</v>
       </c>
       <c r="C16" t="s">
@@ -1624,7 +1624,7 @@
       </c>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>12</v>
       </c>
       <c r="C17" t="s">
@@ -1650,7 +1650,7 @@
       </c>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>13</v>
       </c>
       <c r="C18" t="s">
@@ -1676,7 +1676,7 @@
       </c>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>14</v>
       </c>
       <c r="C19" t="s">
@@ -1702,7 +1702,7 @@
       </c>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>15</v>
       </c>
       <c r="C20" t="s">

--- a/DesignerConfigs/Datas/PayRegion.xlsx
+++ b/DesignerConfigs/Datas/PayRegion.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -260,15 +260,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color rgb="FF333333"/>
       <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -898,11 +898,11 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1251,9 +1251,9 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1266,49 +1266,49 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:10">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1337,23 +1337,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:9">
-      <c r="B6" s="4">
+    <row r="6" spans="1:10">
+      <c r="B6" s="5">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
         <v>2</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="5">
         <v>1</v>
       </c>
       <c r="H6" t="s">
@@ -1363,23 +1363,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:9">
-      <c r="B7" s="4">
+    <row r="7" spans="1:10">
+      <c r="B7" s="5">
         <v>2</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="5">
         <v>2</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="5">
         <v>1.4</v>
       </c>
       <c r="H7" t="s">
@@ -1389,23 +1389,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:9">
-      <c r="B8" s="4">
+    <row r="8" spans="1:10">
+      <c r="B8" s="5">
         <v>3</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="5">
         <v>2</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="5">
         <v>20</v>
       </c>
       <c r="H8" t="s">
@@ -1415,24 +1415,24 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="2:9">
-      <c r="B9" s="4">
+    <row r="9" spans="1:10">
+      <c r="B9" s="5">
         <v>4</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="5">
         <v>2</v>
       </c>
-      <c r="G9" s="4">
-        <v>5</v>
+      <c r="G9" s="5">
+        <v>3</v>
       </c>
       <c r="H9" t="s">
         <v>34</v>
@@ -1441,23 +1441,23 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="2:9">
-      <c r="B10" s="4">
+    <row r="10" spans="1:10">
+      <c r="B10" s="5">
         <v>5</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D10" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="5">
         <v>2</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="5">
         <v>1</v>
       </c>
       <c r="H10" t="s">
@@ -1467,23 +1467,23 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="2:9">
-      <c r="B11" s="4">
+    <row r="11" spans="1:10">
+      <c r="B11" s="5">
         <v>6</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D11" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <v>2</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="5">
         <v>1</v>
       </c>
       <c r="H11" t="s">
@@ -1493,23 +1493,23 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="2:9">
-      <c r="B12" s="4">
+    <row r="12" spans="1:10">
+      <c r="B12" s="5">
         <v>7</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D12" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <v>2</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="5">
         <v>1</v>
       </c>
       <c r="H12" t="s">
@@ -1519,23 +1519,23 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="2:9">
-      <c r="B13" s="4">
+    <row r="13" spans="1:10">
+      <c r="B13" s="5">
         <v>8</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D13" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="5">
         <v>0</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="5">
         <v>150</v>
       </c>
       <c r="H13" t="s">
@@ -1545,23 +1545,23 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="2:9">
-      <c r="B14" s="4">
+    <row r="14" spans="1:10">
+      <c r="B14" s="5">
         <v>9</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>49</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="5">
         <v>2</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="5">
         <v>1.5</v>
       </c>
       <c r="H14" t="s">
@@ -1571,8 +1571,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="2:9">
-      <c r="B15" s="4">
+    <row r="15" spans="1:10">
+      <c r="B15" s="5">
         <v>10</v>
       </c>
       <c r="C15" t="s">
@@ -1584,7 +1584,7 @@
       <c r="E15" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="5">
         <v>0</v>
       </c>
       <c r="G15">
@@ -1597,8 +1597,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="2:9">
-      <c r="B16" s="4">
+    <row r="16" spans="1:10">
+      <c r="B16" s="5">
         <v>11</v>
       </c>
       <c r="C16" t="s">
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="H16" t="s">
         <v>55</v>
@@ -1624,7 +1624,7 @@
       </c>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="4">
+      <c r="B17" s="5">
         <v>12</v>
       </c>
       <c r="C17" t="s">
@@ -1650,7 +1650,7 @@
       </c>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="4">
+      <c r="B18" s="5">
         <v>13</v>
       </c>
       <c r="C18" t="s">
@@ -1676,7 +1676,7 @@
       </c>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="4">
+      <c r="B19" s="5">
         <v>14</v>
       </c>
       <c r="C19" t="s">
@@ -1702,7 +1702,7 @@
       </c>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="4">
+      <c r="B20" s="5">
         <v>15</v>
       </c>
       <c r="C20" t="s">

--- a/DesignerConfigs/Datas/PayRegion.xlsx
+++ b/DesignerConfigs/Datas/PayRegion.xlsx
@@ -100,7 +100,7 @@
     <t>US</t>
   </si>
   <si>
-    <t>0,1,2</t>
+    <t>0,1,13,2</t>
   </si>
   <si>
     <t>$</t>
@@ -127,7 +127,7 @@
     <t>BR</t>
   </si>
   <si>
-    <t>6,4,7</t>
+    <t>0,6,4,7,8</t>
   </si>
   <si>
     <t>R$</t>
@@ -1218,6 +1218,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="13.8833333333333" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
     <col min="7" max="7" width="13.3333333333333" customWidth="1"/>
     <col min="8" max="8" width="25.2166666666667" customWidth="1"/>
     <col min="9" max="9" width="16.875" customWidth="1"/>

--- a/DesignerConfigs/Datas/PayRegion.xlsx
+++ b/DesignerConfigs/Datas/PayRegion.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\_Project\AsWaterGameProj\DesignerConfigs\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -127,7 +132,7 @@
     <t>BR</t>
   </si>
   <si>
-    <t>0,6,4,7,8</t>
+    <t>6,0,4,7,8</t>
   </si>
   <si>
     <t>R$</t>
